--- a/output/pdf_financials_xlsx/MOSS.xlsx
+++ b/output/pdf_financials_xlsx/MOSS.xlsx
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.730391</v>
+        <v>-0.730391</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-0.133037</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.730391</v>
+        <v>-0.730391</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-0.133037</v>
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.730391</v>
+        <v>-0.730391</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-0.133037</v>
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>36.51955</v>
+        <v>-36.51955</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.730391</v>
+        <v>-0.730391</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.133037</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.730391</v>
+        <v>-0.730391</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.133037</v>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -1933,10 +1933,10 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.100188</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.161509</v>
       </c>
     </row>
     <row r="93">
@@ -3083,7 +3083,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -5635,10 +5639,10 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0.730391</v>
+        <v>-0.730391</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.133037</v>
+        <v>-0.133037</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MOSS.xlsx
+++ b/output/pdf_financials_xlsx/MOSS.xlsx
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.017587</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.01174</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.054599</v>
       </c>
     </row>
     <row r="35">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.017587</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.01174</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.054599</v>
       </c>
     </row>
     <row r="37">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.04364</v>
+        <v>0.026053</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.01174</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.150229</v>
+        <v>1.09563</v>
       </c>
     </row>
     <row r="49">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">

--- a/output/pdf_financials_xlsx/MOSS.xlsx
+++ b/output/pdf_financials_xlsx/MOSS.xlsx
@@ -1517,10 +1517,10 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.005575</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="68">
@@ -2065,13 +2065,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.014473</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003749</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.004852</v>
       </c>
     </row>
     <row r="102">
@@ -2145,13 +2145,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.115828</v>
+        <v>-0.130301</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.074965</v>
+        <v>0.071216</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.035778</v>
+        <v>0.030926</v>
       </c>
     </row>
     <row r="107">
@@ -3731,7 +3731,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>-0.014473</v>
       </c>
@@ -3820,7 +3824,11 @@
           <t>Issuance of shares from private placement</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
